--- a/isms-core-framework/A.8-technological-controls/isms-a.8.2-3-5-authentication-privileged-access/WKBK/ISMS-IMP-A.8.2-3-5.S5_Access_Restrictions_Assessment_20260301.xlsx
+++ b/isms-core-framework/A.8-technological-controls/isms-a.8.2-3-5-authentication-privileged-access/WKBK/ISMS-IMP-A.8.2-3-5.S5_Access_Restrictions_Assessment_20260301.xlsx
@@ -719,7 +719,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>01.03.2026 12:12</t>
+          <t>01.03.2026 17:58</t>
         </is>
       </c>
     </row>
